--- a/Raw Data/Stock and Production/MPOB Export 3Y.xlsx
+++ b/Raw Data/Stock and Production/MPOB Export 3Y.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ClaudeCode\Raw Data\Stock and Production\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61BB0121-7DB7-42E9-8CE4-A380054D85C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{810AF165-7700-4716-A34C-C3D9E490E254}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="39735" yWindow="-20490" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table Data" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="dd/m/yyyy;@"/>
+    <numFmt numFmtId="164" formatCode="dd/m/yyyy;@"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -72,7 +72,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -412,14 +412,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B124"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:B125"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.875" customWidth="1"/>
     <col min="2" max="2" width="23.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -427,7 +427,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -435,986 +435,994 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
+        <v>46143</v>
+      </c>
+      <c r="B3">
+        <v>1105760</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
         <v>46113</v>
       </c>
-      <c r="B3">
+      <c r="B4">
         <v>1302979</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="1">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
         <v>46082</v>
       </c>
-      <c r="B4">
+      <c r="B5">
         <v>1521098</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
         <v>46054</v>
       </c>
-      <c r="B5">
+      <c r="B6">
         <v>1102587</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
         <v>46023</v>
       </c>
-      <c r="B6">
+      <c r="B7">
         <v>1454625</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
         <v>45992</v>
       </c>
-      <c r="B7">
+      <c r="B8">
         <v>1331894</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="1">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
         <v>45962</v>
       </c>
-      <c r="B8">
+      <c r="B9">
         <v>1213130</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="1">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
         <v>45931</v>
       </c>
-      <c r="B9">
+      <c r="B10">
         <v>1687495</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A10" s="1">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
         <v>45901</v>
       </c>
-      <c r="B10">
+      <c r="B11">
         <v>1427609</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A11" s="1">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
         <v>45870</v>
       </c>
-      <c r="B11">
+      <c r="B12">
         <v>1325672</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A12" s="1">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
         <v>45839</v>
       </c>
-      <c r="B12">
+      <c r="B13">
         <v>1328547</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A13" s="1">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
         <v>45809</v>
       </c>
-      <c r="B13">
+      <c r="B14">
         <v>1260930</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="1">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
         <v>45778</v>
       </c>
-      <c r="B14">
+      <c r="B15">
         <v>1407411</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A15" s="1">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
         <v>45748</v>
       </c>
-      <c r="B15">
+      <c r="B16">
         <v>1104333</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A16" s="1">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
         <v>45717</v>
       </c>
-      <c r="B16">
+      <c r="B17">
         <v>1005547</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A17" s="1">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
         <v>45689</v>
       </c>
-      <c r="B17">
+      <c r="B18">
         <v>996460</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A18" s="1">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
         <v>45658</v>
       </c>
-      <c r="B18">
+      <c r="B19">
         <v>1196849</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A19" s="1">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
         <v>45627</v>
       </c>
-      <c r="B19">
+      <c r="B20">
         <v>1341936</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A20" s="1">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="1">
         <v>45597</v>
       </c>
-      <c r="B20">
+      <c r="B21">
         <v>1490293</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A21" s="1">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
         <v>45566</v>
       </c>
-      <c r="B21">
+      <c r="B22">
         <v>1744265</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A22" s="1">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" s="1">
         <v>45536</v>
       </c>
-      <c r="B22">
+      <c r="B23">
         <v>1559846</v>
       </c>
     </row>
-    <row r="23" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A23" s="1">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="1">
         <v>45505</v>
       </c>
-      <c r="B23">
+      <c r="B24">
         <v>1528632</v>
       </c>
     </row>
-    <row r="24" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A24" s="1">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" s="1">
         <v>45474</v>
       </c>
-      <c r="B24">
+      <c r="B25">
         <v>1689710</v>
       </c>
     </row>
-    <row r="25" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A25" s="1">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" s="1">
         <v>45444</v>
       </c>
-      <c r="B25">
+      <c r="B26">
         <v>1207414</v>
       </c>
     </row>
-    <row r="26" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A26" s="1">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" s="1">
         <v>45413</v>
       </c>
-      <c r="B26">
+      <c r="B27">
         <v>1382429</v>
       </c>
     </row>
-    <row r="27" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A27" s="1">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" s="1">
         <v>45383</v>
       </c>
-      <c r="B27">
+      <c r="B28">
         <v>1234208</v>
       </c>
     </row>
-    <row r="28" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A28" s="1">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" s="1">
         <v>45352</v>
       </c>
-      <c r="B28">
+      <c r="B29">
         <v>1317628</v>
       </c>
     </row>
-    <row r="29" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A29" s="1">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" s="1">
         <v>45323</v>
       </c>
-      <c r="B29">
+      <c r="B30">
         <v>1015537</v>
       </c>
     </row>
-    <row r="30" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A30" s="1">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" s="1">
         <v>45292</v>
       </c>
-      <c r="B30">
+      <c r="B31">
         <v>1350574</v>
       </c>
     </row>
-    <row r="31" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A31" s="1">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" s="1">
         <v>45261</v>
       </c>
-      <c r="B31">
+      <c r="B32">
         <v>1334441</v>
       </c>
     </row>
-    <row r="32" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A32" s="1">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" s="1">
         <v>45231</v>
       </c>
-      <c r="B32">
+      <c r="B33">
         <v>1396721</v>
       </c>
     </row>
-    <row r="33" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A33" s="1">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" s="1">
         <v>45200</v>
       </c>
-      <c r="B33">
+      <c r="B34">
         <v>1466065</v>
       </c>
     </row>
-    <row r="34" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A34" s="1">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" s="1">
         <v>45170</v>
       </c>
-      <c r="B34">
+      <c r="B35">
         <v>1196113</v>
       </c>
     </row>
-    <row r="35" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A35" s="1">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" s="1">
         <v>45139</v>
       </c>
-      <c r="B35">
+      <c r="B36">
         <v>1221848</v>
       </c>
     </row>
-    <row r="36" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A36" s="1">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" s="1">
         <v>45108</v>
       </c>
-      <c r="B36">
+      <c r="B37">
         <v>1354336</v>
       </c>
     </row>
-    <row r="37" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A37" s="1">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" s="1">
         <v>45078</v>
       </c>
-      <c r="B37">
+      <c r="B38">
         <v>1171741</v>
       </c>
     </row>
-    <row r="38" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A38" s="1">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" s="1">
         <v>45047</v>
       </c>
-      <c r="B38">
+      <c r="B39">
         <v>1079020</v>
       </c>
     </row>
-    <row r="39" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A39" s="1">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" s="1">
         <v>45017</v>
       </c>
-      <c r="B39">
+      <c r="B40">
         <v>1087541</v>
       </c>
     </row>
-    <row r="40" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A40" s="1">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" s="1">
         <v>44986</v>
       </c>
-      <c r="B40">
+      <c r="B41">
         <v>1487836</v>
       </c>
     </row>
-    <row r="41" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A41" s="1">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42" s="1">
         <v>44958</v>
       </c>
-      <c r="B41">
+      <c r="B42">
         <v>1127953</v>
       </c>
     </row>
-    <row r="42" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A42" s="1">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43" s="1">
         <v>44927</v>
       </c>
-      <c r="B42">
+      <c r="B43">
         <v>1137005</v>
       </c>
     </row>
-    <row r="43" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A43" s="1">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44" s="1">
         <v>44896</v>
       </c>
-      <c r="B43">
+      <c r="B44">
         <v>1473846</v>
       </c>
     </row>
-    <row r="44" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A44" s="1">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45" s="1">
         <v>44866</v>
       </c>
-      <c r="B44">
+      <c r="B45">
         <v>1521329</v>
       </c>
     </row>
-    <row r="45" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A45" s="1">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46" s="1">
         <v>44835</v>
       </c>
-      <c r="B45">
+      <c r="B46">
         <v>1503835</v>
       </c>
     </row>
-    <row r="46" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A46" s="1">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47" s="1">
         <v>44805</v>
       </c>
-      <c r="B46">
+      <c r="B47">
         <v>1423195</v>
       </c>
     </row>
-    <row r="47" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A47" s="1">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48" s="1">
         <v>44774</v>
       </c>
-      <c r="B47">
+      <c r="B48">
         <v>1299930</v>
       </c>
     </row>
-    <row r="48" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A48" s="1">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49" s="1">
         <v>44743</v>
       </c>
-      <c r="B48">
+      <c r="B49">
         <v>1325342</v>
       </c>
     </row>
-    <row r="49" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A49" s="1">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50" s="1">
         <v>44713</v>
       </c>
-      <c r="B49">
+      <c r="B50">
         <v>1193928</v>
       </c>
     </row>
-    <row r="50" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A50" s="1">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A51" s="1">
         <v>44682</v>
       </c>
-      <c r="B50">
+      <c r="B51">
         <v>1376416</v>
       </c>
     </row>
-    <row r="51" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A51" s="1">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A52" s="1">
         <v>44652</v>
       </c>
-      <c r="B51">
+      <c r="B52">
         <v>1054550</v>
       </c>
     </row>
-    <row r="52" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A52" s="1">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A53" s="1">
         <v>44621</v>
       </c>
-      <c r="B52">
+      <c r="B53">
         <v>1265379</v>
       </c>
     </row>
-    <row r="53" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A53" s="1">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A54" s="1">
         <v>44593</v>
       </c>
-      <c r="B53">
+      <c r="B54">
         <v>1108576</v>
       </c>
     </row>
-    <row r="54" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A54" s="1">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A55" s="1">
         <v>44562</v>
       </c>
-      <c r="B54">
+      <c r="B55">
         <v>1157976</v>
       </c>
     </row>
-    <row r="55" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A55" s="1">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A56" s="1">
         <v>44531</v>
       </c>
-      <c r="B55">
+      <c r="B56">
         <v>1414566</v>
       </c>
     </row>
-    <row r="56" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A56" s="1">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A57" s="1">
         <v>44501</v>
       </c>
-      <c r="B56">
+      <c r="B57">
         <v>1467518</v>
       </c>
     </row>
-    <row r="57" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A57" s="1">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A58" s="1">
         <v>44470</v>
       </c>
-      <c r="B57">
+      <c r="B58">
         <v>1417868</v>
       </c>
     </row>
-    <row r="58" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A58" s="1">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A59" s="1">
         <v>44440</v>
       </c>
-      <c r="B58">
+      <c r="B59">
         <v>1597393</v>
       </c>
     </row>
-    <row r="59" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A59" s="1">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A60" s="1">
         <v>44409</v>
       </c>
-      <c r="B59">
+      <c r="B60">
         <v>1167425</v>
       </c>
     </row>
-    <row r="60" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A60" s="1">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A61" s="1">
         <v>44378</v>
       </c>
-      <c r="B60">
+      <c r="B61">
         <v>1408321</v>
       </c>
     </row>
-    <row r="61" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A61" s="1">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A62" s="1">
         <v>44348</v>
       </c>
-      <c r="B61">
+      <c r="B62">
         <v>1418825</v>
       </c>
     </row>
-    <row r="62" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A62" s="1">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A63" s="1">
         <v>44317</v>
       </c>
-      <c r="B62">
+      <c r="B63">
         <v>1265460</v>
       </c>
     </row>
-    <row r="63" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A63" s="1">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A64" s="1">
         <v>44287</v>
       </c>
-      <c r="B63">
+      <c r="B64">
         <v>1338672</v>
       </c>
     </row>
-    <row r="64" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A64" s="1">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A65" s="1">
         <v>44256</v>
       </c>
-      <c r="B64">
+      <c r="B65">
         <v>1182084</v>
       </c>
     </row>
-    <row r="65" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A65" s="1">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A66" s="1">
         <v>44228</v>
       </c>
-      <c r="B65">
+      <c r="B66">
         <v>895556</v>
       </c>
     </row>
-    <row r="66" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A66" s="1">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A67" s="1">
         <v>44197</v>
       </c>
-      <c r="B66">
+      <c r="B67">
         <v>947395</v>
       </c>
     </row>
-    <row r="67" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A67" s="1">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A68" s="1">
         <v>44166</v>
       </c>
-      <c r="B67">
+      <c r="B68">
         <v>1642835</v>
       </c>
     </row>
-    <row r="68" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A68" s="1">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A69" s="1">
         <v>44136</v>
       </c>
-      <c r="B68">
+      <c r="B69">
         <v>1303318</v>
       </c>
     </row>
-    <row r="69" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A69" s="1">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A70" s="1">
         <v>44105</v>
       </c>
-      <c r="B69">
+      <c r="B70">
         <v>1674304</v>
       </c>
     </row>
-    <row r="70" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A70" s="1">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A71" s="1">
         <v>44075</v>
       </c>
-      <c r="B70">
+      <c r="B71">
         <v>1612155</v>
       </c>
     </row>
-    <row r="71" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A71" s="1">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A72" s="1">
         <v>44044</v>
       </c>
-      <c r="B71">
+      <c r="B72">
         <v>1581612</v>
       </c>
     </row>
-    <row r="72" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A72" s="1">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A73" s="1">
         <v>44013</v>
       </c>
-      <c r="B72">
+      <c r="B73">
         <v>1782276</v>
       </c>
     </row>
-    <row r="73" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A73" s="1">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A74" s="1">
         <v>43983</v>
       </c>
-      <c r="B73">
+      <c r="B74">
         <v>1710597</v>
       </c>
     </row>
-    <row r="74" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A74" s="1">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A75" s="1">
         <v>43952</v>
       </c>
-      <c r="B74">
+      <c r="B75">
         <v>1368746</v>
       </c>
     </row>
-    <row r="75" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A75" s="1">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A76" s="1">
         <v>43922</v>
       </c>
-      <c r="B75">
+      <c r="B76">
         <v>1236438</v>
       </c>
     </row>
-    <row r="76" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A76" s="1">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A77" s="1">
         <v>43891</v>
       </c>
-      <c r="B76">
+      <c r="B77">
         <v>1184702</v>
       </c>
     </row>
-    <row r="77" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A77" s="1">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A78" s="1">
         <v>43862</v>
       </c>
-      <c r="B77">
+      <c r="B78">
         <v>1082417</v>
       </c>
     </row>
-    <row r="78" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A78" s="1">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A79" s="1">
         <v>43831</v>
       </c>
-      <c r="B78">
+      <c r="B79">
         <v>1213539</v>
       </c>
     </row>
-    <row r="79" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A79" s="1">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A80" s="1">
         <v>43800</v>
       </c>
-      <c r="B79">
+      <c r="B80">
         <v>1396157</v>
       </c>
     </row>
-    <row r="80" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A80" s="1">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A81" s="1">
         <v>43770</v>
       </c>
-      <c r="B80">
+      <c r="B81">
         <v>1405638</v>
       </c>
     </row>
-    <row r="81" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A81" s="1">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A82" s="1">
         <v>43739</v>
       </c>
-      <c r="B81">
+      <c r="B82">
         <v>1641839</v>
       </c>
     </row>
-    <row r="82" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A82" s="1">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A83" s="1">
         <v>43709</v>
       </c>
-      <c r="B82">
+      <c r="B83">
         <v>1409945</v>
       </c>
     </row>
-    <row r="83" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A83" s="1">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A84" s="1">
         <v>43678</v>
       </c>
-      <c r="B83">
+      <c r="B84">
         <v>1732888</v>
       </c>
     </row>
-    <row r="84" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A84" s="1">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A85" s="1">
         <v>43647</v>
       </c>
-      <c r="B84">
+      <c r="B85">
         <v>1489171</v>
       </c>
     </row>
-    <row r="85" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A85" s="1">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A86" s="1">
         <v>43617</v>
       </c>
-      <c r="B85">
+      <c r="B86">
         <v>1383216</v>
       </c>
     </row>
-    <row r="86" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A86" s="1">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A87" s="1">
         <v>43586</v>
       </c>
-      <c r="B86">
+      <c r="B87">
         <v>1714567</v>
       </c>
     </row>
-    <row r="87" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A87" s="1">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A88" s="1">
         <v>43556</v>
       </c>
-      <c r="B87">
+      <c r="B88">
         <v>1651249</v>
       </c>
     </row>
-    <row r="88" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A88" s="1">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A89" s="1">
         <v>43525</v>
       </c>
-      <c r="B88">
+      <c r="B89">
         <v>1618545</v>
       </c>
     </row>
-    <row r="89" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A89" s="1">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A90" s="1">
         <v>43497</v>
       </c>
-      <c r="B89">
+      <c r="B90">
         <v>1321946</v>
       </c>
     </row>
-    <row r="90" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A90" s="1">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A91" s="1">
         <v>43466</v>
       </c>
-      <c r="B90">
+      <c r="B91">
         <v>1680669</v>
       </c>
     </row>
-    <row r="91" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A91" s="1">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A92" s="1">
         <v>43435</v>
       </c>
-      <c r="B91">
+      <c r="B92">
         <v>1383307</v>
       </c>
     </row>
-    <row r="92" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A92" s="1">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A93" s="1">
         <v>43405</v>
       </c>
-      <c r="B92">
+      <c r="B93">
         <v>1375406</v>
       </c>
     </row>
-    <row r="93" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A93" s="1">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A94" s="1">
         <v>43374</v>
       </c>
-      <c r="B93">
+      <c r="B94">
         <v>1578263</v>
       </c>
     </row>
-    <row r="94" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A94" s="1">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A95" s="1">
         <v>43344</v>
       </c>
-      <c r="B94">
+      <c r="B95">
         <v>1619317</v>
       </c>
     </row>
-    <row r="95" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A95" s="1">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A96" s="1">
         <v>43313</v>
       </c>
-      <c r="B95">
+      <c r="B96">
         <v>1099583</v>
       </c>
     </row>
-    <row r="96" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A96" s="1">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A97" s="1">
         <v>43282</v>
       </c>
-      <c r="B96">
+      <c r="B97">
         <v>1196651</v>
       </c>
     </row>
-    <row r="97" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A97" s="1">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A98" s="1">
         <v>43252</v>
       </c>
-      <c r="B97">
+      <c r="B98">
         <v>1129088</v>
       </c>
     </row>
-    <row r="98" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A98" s="1">
+    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A99" s="1">
         <v>43221</v>
       </c>
-      <c r="B98">
+      <c r="B99">
         <v>1290601</v>
       </c>
     </row>
-    <row r="99" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A99" s="1">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A100" s="1">
         <v>43191</v>
       </c>
-      <c r="B99">
+      <c r="B100">
         <v>1530139</v>
       </c>
     </row>
-    <row r="100" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A100" s="1">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A101" s="1">
         <v>43160</v>
       </c>
-      <c r="B100">
+      <c r="B101">
         <v>1565317</v>
       </c>
     </row>
-    <row r="101" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A101" s="1">
+    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A102" s="1">
         <v>43132</v>
       </c>
-      <c r="B101">
+      <c r="B102">
         <v>1313136</v>
       </c>
     </row>
-    <row r="102" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A102" s="1">
+    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A103" s="1">
         <v>43101</v>
       </c>
-      <c r="B102">
+      <c r="B103">
         <v>1513239</v>
       </c>
     </row>
-    <row r="103" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A103" s="1">
+    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A104" s="1">
         <v>43070</v>
       </c>
-      <c r="B103">
+      <c r="B104">
         <v>1427425</v>
       </c>
     </row>
-    <row r="104" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A104" s="1">
+    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A105" s="1">
         <v>43040</v>
       </c>
-      <c r="B104">
+      <c r="B105">
         <v>1356378</v>
       </c>
     </row>
-    <row r="105" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A105" s="1">
+    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A106" s="1">
         <v>43009</v>
       </c>
-      <c r="B105">
+      <c r="B106">
         <v>1538050</v>
       </c>
     </row>
-    <row r="106" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A106" s="1">
+    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A107" s="1">
         <v>42979</v>
       </c>
-      <c r="B106">
+      <c r="B107">
         <v>1517783</v>
       </c>
     </row>
-    <row r="107" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A107" s="1">
+    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A108" s="1">
         <v>42948</v>
       </c>
-      <c r="B107">
+      <c r="B108">
         <v>1487820</v>
       </c>
     </row>
-    <row r="108" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A108" s="1">
+    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A109" s="1">
         <v>42917</v>
       </c>
-      <c r="B108">
+      <c r="B109">
         <v>1397910</v>
       </c>
     </row>
-    <row r="109" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A109" s="1">
+    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A110" s="1">
         <v>42887</v>
       </c>
-      <c r="B109">
+      <c r="B110">
         <v>1379720</v>
       </c>
     </row>
-    <row r="110" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A110" s="1">
+    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A111" s="1">
         <v>42856</v>
       </c>
-      <c r="B110">
+      <c r="B111">
         <v>1506056</v>
       </c>
     </row>
-    <row r="111" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A111" s="1">
+    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A112" s="1">
         <v>42826</v>
       </c>
-      <c r="B111">
+      <c r="B112">
         <v>1283308</v>
       </c>
     </row>
-    <row r="112" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A112" s="1">
+    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A113" s="1">
         <v>42795</v>
       </c>
-      <c r="B112">
+      <c r="B113">
         <v>1265771</v>
       </c>
     </row>
-    <row r="113" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A113" s="1">
+    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A114" s="1">
         <v>42767</v>
       </c>
-      <c r="B113">
+      <c r="B114">
         <v>1107018</v>
       </c>
     </row>
-    <row r="114" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A114" s="1">
+    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A115" s="1">
         <v>42736</v>
       </c>
-      <c r="B114">
+      <c r="B115">
         <v>1286800</v>
       </c>
     </row>
-    <row r="115" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A115" s="1">
+    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A116" s="1">
         <v>42705</v>
       </c>
-      <c r="B115">
+      <c r="B116">
         <v>1267941</v>
       </c>
     </row>
-    <row r="116" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A116" s="1">
+    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A117" s="1">
         <v>42675</v>
       </c>
-      <c r="B116">
+      <c r="B117">
         <v>1370411</v>
       </c>
     </row>
-    <row r="117" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A117" s="1">
+    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A118" s="1">
         <v>42644</v>
       </c>
-      <c r="B117">
+      <c r="B118">
         <v>1431129</v>
       </c>
     </row>
-    <row r="118" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A118" s="1">
+    <row r="119" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A119" s="1">
         <v>42614</v>
       </c>
-      <c r="B118">
+      <c r="B119">
         <v>1451144</v>
       </c>
     </row>
-    <row r="119" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A119" s="1">
+    <row r="120" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A120" s="1">
         <v>42583</v>
       </c>
-      <c r="B119">
+      <c r="B120">
         <v>1823612</v>
       </c>
     </row>
-    <row r="120" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A120" s="1">
+    <row r="121" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A121" s="1">
         <v>42552</v>
       </c>
-      <c r="B120">
+      <c r="B121">
         <v>1384220</v>
       </c>
     </row>
-    <row r="121" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A121" s="1">
+    <row r="122" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A122" s="1">
         <v>42522</v>
       </c>
-      <c r="B121">
+      <c r="B122">
         <v>1141673</v>
       </c>
     </row>
-    <row r="122" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A122" s="1">
+    <row r="123" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A123" s="1">
         <v>42491</v>
       </c>
-      <c r="B122">
+      <c r="B123">
         <v>1282415</v>
       </c>
     </row>
-    <row r="123" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A123" s="1">
+    <row r="124" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A124" s="1">
         <v>42461</v>
       </c>
-      <c r="B123">
+      <c r="B124">
         <v>1172915</v>
       </c>
     </row>
-    <row r="124" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A124" s="1">
+    <row r="125" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A125" s="1">
         <v>42430</v>
       </c>
-      <c r="B124">
+      <c r="B125">
         <v>1334419</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A5:B124 A1:B2 A4" numberStoredAsText="1"/>
+    <ignoredError sqref="A6:B125 A1:B2 A5" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>